--- a/数据/北环高速现状桥梁隧道统计.xlsx
+++ b/数据/北环高速现状桥梁隧道统计.xlsx
@@ -133,7 +133,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>双向</t>
+    <t>双向双洞，长度按路线计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -741,8 +741,8 @@
         <v>20</v>
       </c>
       <c r="D10" s="3">
-        <f>(11210-9860)/1000*2</f>
-        <v>2.7</v>
+        <f>(11210-9860)/1000</f>
+        <v>1.35</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>24</v>
